--- a/context_DB/SSD_context_db.xlsx
+++ b/context_DB/SSD_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL79"/>
+  <dimension ref="A1:BM79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,65 +686,70 @@
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
+          <t>fatalities</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>event_count_evt2</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>ADM1_PCODE_evt2</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>ADM3_PCODE_evt2</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>sub_event_type</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>actor1</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>actor2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_2</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
           <t>admin2</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>fatalities</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>event_count_evt2</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>ADM3_PCODE_evt2</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>event_type</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>sub_event_type</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>actor1</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_1</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>actor2</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_2</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>event_date</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>ratio IDP/ToTN - HPC2025</t>
         </is>
@@ -767,7 +772,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -858,7 +863,8 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="n">
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="n">
         <v>0.6120965577054123</v>
       </c>
     </row>
@@ -879,7 +885,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1024,59 +1030,64 @@
           <t>Central Equatoria</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>Juba</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1</v>
       </c>
       <c r="BA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>SS01</t>
+        </is>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>Protests ---- Strategic developments ---- Strategic developments ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Protests ---- Riots ---- Riots ---- Riots ---- Strategic developments</t>
+          <t>Strategic developments ---- Riots ---- Riots ---- Riots ---- Protests ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Strategic developments ---- Strategic developments ---- Protests ---- Protests</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Arrests ---- Other ---- Sexual violence ---- Protest with intervention ---- Attack ---- Peaceful protest ---- Violent demonstration ---- Violent demonstration ---- Violent demonstration ---- Other</t>
+          <t>Other ---- Violent demonstration ---- Violent demonstration ---- Violent demonstration ---- Peaceful protest ---- Attack ---- Protest with intervention ---- Sexual violence ---- Other ---- Arrests ---- Peaceful protest ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>Protesters (South Sudan) ---- Police Forces of South Sudan (2011-) National Security Service ---- Government of South Sudan (2011-) ---- Unidentified Armed Group (South Sudan) ---- Protesters (South Sudan) ---- Unidentified Armed Group (South Sudan) ---- Protesters (South Sudan) ---- Rioters (South Sudan) ---- Rioters (South Sudan) ---- Rioters (South Sudan) ---- Government of South Sudan (2011-)</t>
+          <t>Government of South Sudan (2011-) ---- Rioters (South Sudan) ---- Rioters (South Sudan) ---- Rioters (South Sudan) ---- Protesters (South Sudan) ---- Unidentified Armed Group (South Sudan) ---- Protesters (South Sudan) ---- Unidentified Armed Group (South Sudan) ---- Government of South Sudan (2011-) ---- Police Forces of South Sudan (2011-) National Security Service ---- Protesters (South Sudan) ---- Protesters (South Sudan)</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Students (South Sudan) ---- Students (South Sudan) ---- Teachers (South Sudan) ---- Students (South Sudan) ---- Students (South Sudan) ---- Students (South Sudan); Women (South Sudan)</t>
+          <t>Students (South Sudan) ---- Students (South Sudan) ---- Students (South Sudan); Women (South Sudan) ---- Teachers (South Sudan) ---- Students (South Sudan) ---- Students (South Sudan) ---- Students (South Sudan)</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>SPLM-In Opposition: Sudan People's Liberation Movement-In Opposition ---- SPLM: Sudan People's Liberation Movement ---- Civilians (South Sudan) ---- Police Forces of South Sudan (2011-) ---- Civilians (South Sudan) ---- Police Forces of South Sudan (2011-) ---- Police Forces of South Sudan (2011-) ---- Police Forces of South Sudan (2011-)</t>
+          <t>Police Forces of South Sudan (2011-) ---- Police Forces of South Sudan (2011-) ---- Police Forces of South Sudan (2011-) ---- Civilians (South Sudan) ---- Police Forces of South Sudan (2011-) ---- Civilians (South Sudan) ---- SPLM: Sudan People's Liberation Movement ---- SPLM-In Opposition: Sudan People's Liberation Movement-In Opposition</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Students (South Sudan); Women (South Sudan) ---- Bari Ethnic Group (South Sudan) ---- Civilians (South Sudan); Teachers (South Sudan)</t>
+          <t>Civilians (South Sudan); Teachers (South Sudan) ---- Bari Ethnic Group (South Sudan) ---- Students (South Sudan); Women (South Sudan)</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>On 2 May 2025, scholarship students protested in front of the GPOC oil company in Hai Kator area of Kator Payam, Juba County (location coded to Kator, the nearest known location in Juba County, Central Equatoria State), over unpaid fees and welfare payments. ---- On 27 April 2025, security officers suspected to be from the NSS arrested Gattuor Kier, the SPLM/A-IO students wing secretary-general, at an unspecified location (location coded to Juba, the country's capital in Juba County, Central Equatoria State). The reason for the arrest is unclear, but it is suspected to be linked to Kier's defiance to endorse an SPLM/A-IO interim leadership formed after the arrest of Riek Machar, the country's First Vice President and SPLM/A-IO leader. ---- Other: On 20 January 2025, President Salva Kiir issued several decrees aired on the state-owned South Sudan Broadcasting Corporation (SSBC) in Juba (Juba, Central Equatoria), where he reshuffled SPLM officials in the Northern Bahr el-Ghazal State government and revoked the appointments of certain lawmakers in the State Parliament. Key officials relieved duties included the Advisor on Legal Affairs and Ministers of Information, Finance, Education, and Animal Resources. New appointments were made for these positions. Several commission members were replaced, including those in the Human Rights and HIV/AIDS Commissions. ---- On 19 November 2024, unidentified individuals suspected to be landgrabbers (coded as unidentified armed group) sexually assaulted and then killed a 19-year-old female student in Molobur area of Jebel Lado Payam (location coded to Jebel Lado in Northern Bari, Juba County, Central Equatoria State). The victim had stepped out of a classroom where she was studying with her friends when the incident happened. ---- On 25 October 2024, (as reported) an unspecified number of students from Nile Modern Secondary School held a protest along Kokora Road in Juba (location coded to Juba in Juba County, Central Equatoria State), against an unspecified cause. The protest turned violent (further details unknown/not reported) leading police to intervene by firing shots in the air. Normalcy later returned to the area. ---- On 15 August 2024, an unknown individual (coded as unidentified armed group) assaulted a Bari community member at Bori Primary School in Northern Bari payam (location coded to Kenyi, Juba county, Central Equatoria state) over a land dispute. ---- On 23 July 2024, teachers protested over salary arrears along the Custom Konyokonyo road in Custom Market (Juba, Central Equatoria). Further information notes that traffic police intervened (through unspecified means) and the protest remained peaceful. ---- On 12 June 2024, a group of students from the University of Juba rallied against an increase of hostel fees in Hai-Thora village near Hai Jebel (Juba, Central Equatoria). Demonstrators clashed with police, an unspecified number of students were arrested, and 5 injuries were reported. ---- On 12 June 2024, a group of students from the University of Juba demonstrated against an increase of hostel fees in Hai-Thora village in Juba (Juba, Central Equatoria). Demonstrators clashed with police, an unspecified number of students were arrested, and 5 injuries were reported. ---- On 12 June 2024, female students demonstrated against the university's proposed increase in hostel fees and demanded improvements in living conditions at the University of Juba (Juba county, Central Equatoria state). The students pelted stones at the police and the Dean of Student Affairs. At least 24 students were beaten with gun butts and sustained injuries such as broken teeth, arm and leg fractures, and other physical injuries. 3 students were receiving treatment at a hospital. An unspecified number of police were also wounded. The police fired gunshots into the air. 73 students were detained and released on the same day. Personal belongings and parts of the facilities were damaged. ---- Other: On 17 May 2024, the President of South Sudan issued a decree in Juba (Juba county, Central Equatoria), resulting in a reshuffle of officials in Warrap State. The changes included the dismissal and appointment of a state advisor on peace and security, the ministers of Parliamentary and Legal Affairs, Youth Culture and Sports, Trade and Industry, Roads and Bridges, and General Education. Additionally, the Deputy Chairperson of the Anti-Corruption Commission, the Chairperson of the Relief and Rehabilitation Commission, and a member of the Relief and Rehabilitation Commission were replaced. Two county commissioners, the commissioners of Gogrial East and Tonj North counties, as well as the Governor of Unity state and chief of Ruweng Administrative Area, were also dismissed and replaced.</t>
+          <t>Other: On 17 May 2024, the President of South Sudan issued a decree in Juba (Juba county, Central Equatoria), resulting in a reshuffle of officials in Warrap State. The changes included the dismissal and appointment of a state advisor on peace and security, the ministers of Parliamentary and Legal Affairs, Youth Culture and Sports, Trade and Industry, Roads and Bridges, and General Education. Additionally, the Deputy Chairperson of the Anti-Corruption Commission, the Chairperson of the Relief and Rehabilitation Commission, and a member of the Relief and Rehabilitation Commission were replaced. Two county commissioners, the commissioners of Gogrial East and Tonj North counties, as well as the Governor of Unity state and chief of Ruweng Administrative Area, were also dismissed and replaced. ---- On 12 June 2024, a group of students from the University of Juba rallied against an increase of hostel fees in Hai-Thora village near Hai Jebel (Juba, Central Equatoria). Demonstrators clashed with police, an unspecified number of students were arrested, and 5 injuries were reported. ---- On 12 June 2024, a group of students from the University of Juba demonstrated against an increase of hostel fees in Hai-Thora village in Juba (Juba, Central Equatoria). Demonstrators clashed with police, an unspecified number of students were arrested, and 5 injuries were reported. ---- On 12 June 2024, female students demonstrated against the university's proposed increase in hostel fees and demanded improvements in living conditions at the University of Juba (Juba county, Central Equatoria state). The students pelted stones at the police and the Dean of Student Affairs. At least 24 students were beaten with gun butts and sustained injuries such as broken teeth, arm and leg fractures, and other physical injuries. 3 students were receiving treatment at a hospital. An unspecified number of police were also wounded. The police fired gunshots into the air. 73 students were detained and released on the same day. Personal belongings and parts of the facilities were damaged. ---- On 23 July 2024, teachers protested over salary arrears along the Custom Konyokonyo road in Custom Market (Juba, Central Equatoria). Further information notes that traffic police intervened (through unspecified means) and the protest remained peaceful. ---- On 15 August 2024, an unknown individual (coded as unidentified armed group) assaulted a Bari community member at Bori Primary School in Northern Bari payam (location coded to Kenyi, Juba county, Central Equatoria state) over a land dispute. ---- On 25 October 2024, (as reported) an unspecified number of students from Nile Modern Secondary School held a protest along Kokora Road in Juba (location coded to Juba in Juba County, Central Equatoria State), against an unspecified cause. The protest turned violent (further details unknown/not reported) leading police to intervene by firing shots in the air. Normalcy later returned to the area. ---- On 19 November 2024, unidentified individuals suspected to be landgrabbers (coded as unidentified armed group) sexually assaulted and then killed a 19-year-old female student in Molobur area of Jebel Lado Payam (location coded to Jebel Lado in Northern Bari, Juba County, Central Equatoria State). The victim had stepped out of a classroom where she was studying with her friends when the incident happened. ---- Other: On 20 January 2025, President Salva Kiir issued several decrees aired on the state-owned South Sudan Broadcasting Corporation (SSBC) in Juba (Juba, Central Equatoria), where he reshuffled SPLM officials in the Northern Bahr el-Ghazal State government and revoked the appointments of certain lawmakers in the State Parliament. Key officials relieved duties included the Advisor on Legal Affairs and Ministers of Information, Finance, Education, and Animal Resources. New appointments were made for these positions. Several commission members were replaced, including those in the Human Rights and HIV/AIDS Commissions. ---- On 27 April 2025, security officers suspected to be from the NSS arrested Gattuor Kier, the SPLM/A-IO students wing secretary-general, at an unspecified location (location coded to Juba, the country's capital in Juba County, Central Equatoria State). The reason for the arrest is unclear, but it is suspected to be linked to Kier's defiance to endorse an SPLM/A-IO interim leadership formed after the arrest of Riek Machar, the country's First Vice President and SPLM/A-IO leader. ---- On 2 May 2025, scholarship students protested in front of the GPOC oil company in Hai Kator area of Kator Payam, Juba County (location coded to Kator, the nearest known location in Juba County, Central Equatoria State), over unpaid fees and welfare payments. The students were arrested and later released (further information unknown/not reported). ---- On 31 July 2025, students at the University of Juba protested in Atlabara, Juba County (Juba, Central Equatoria), over a suspected Ugandan military incursion into Kajo Keji County.</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>02 May 2025 ---- 27 April 2025 ---- 20 January 2025 ---- 19 November 2024 ---- 25 October 2024 ---- 15 August 2024 ---- 23 July 2024 ---- 12 June 2024 ---- 12 June 2024 ---- 12 June 2024 ---- 17 May 2024</t>
-        </is>
-      </c>
-      <c r="BL3" t="n">
+          <t>2024-05-17 ---- 2024-06-12 ---- 2024-06-12 ---- 2024-06-12 ---- 2024-07-23 ---- 2024-08-15 ---- 2024-10-25 ---- 2024-11-19 ---- 2025-01-20 ---- 2025-04-27 ---- 2025-05-02 ---- 2025-07-31</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>Juba</t>
+        </is>
+      </c>
+      <c r="BM3" t="n">
         <v>0.3483104775536257</v>
       </c>
     </row>
@@ -1097,7 +1108,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1188,7 +1199,8 @@
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="n">
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="n">
         <v>0.0741768330001224</v>
       </c>
     </row>
@@ -1209,7 +1221,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1292,16 +1304,16 @@
           <t>Central Equatoria</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>Lainya</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB5" t="n">
         <v>1</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>SS01</t>
+        </is>
       </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr">
@@ -1333,10 +1345,15 @@
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>04 February 2024</t>
-        </is>
-      </c>
-      <c r="BL5" t="n">
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>Lainya</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
         <v>0.08849117573949788</v>
       </c>
     </row>
@@ -1352,12 +1369,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SS0105</t>
+          <t>SS0101</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1448,7 +1465,8 @@
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="n">
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="n">
         <v>0.09758408337280909</v>
       </c>
     </row>
@@ -1469,7 +1487,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1552,16 +1570,16 @@
           <t>Central Equatoria</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>Terekeka</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB7" t="n">
         <v>1</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>SS01</t>
+        </is>
       </c>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr">
@@ -1601,10 +1619,15 @@
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>11 April 2025</t>
-        </is>
-      </c>
-      <c r="BL7" t="n">
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>Terekeka</t>
+        </is>
+      </c>
+      <c r="BM7" t="n">
         <v>0.05762188705717292</v>
       </c>
     </row>
@@ -1625,7 +1648,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1770,16 +1793,16 @@
           <t>Central Equatoria</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>Yei</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
       </c>
-      <c r="BB8" t="n">
-        <v>1</v>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>SS01</t>
+        </is>
       </c>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr">
@@ -1811,10 +1834,15 @@
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>08 November 2024</t>
-        </is>
-      </c>
-      <c r="BL8" t="n">
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>Yei</t>
+        </is>
+      </c>
+      <c r="BM8" t="n">
         <v>0.1582089881688151</v>
       </c>
     </row>
@@ -1835,7 +1863,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SS0201;SS0207;SS0300;SS0602;SS0703;SS1001;SS1005;SS1008</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1918,16 +1946,16 @@
           <t>Eastern Equatoria</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>Budi</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1</v>
       </c>
       <c r="BA9" t="n">
         <v>1</v>
       </c>
-      <c r="BB9" t="n">
-        <v>1</v>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>SS02</t>
+        </is>
       </c>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr">
@@ -1959,10 +1987,15 @@
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>19 January 2024</t>
-        </is>
-      </c>
-      <c r="BL9" t="n">
+          <t>2024-01-19</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>Budi</t>
+        </is>
+      </c>
+      <c r="BM9" t="n">
         <v>0.04653618931317866</v>
       </c>
     </row>
@@ -1983,7 +2016,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2074,7 +2107,8 @@
       <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="inlineStr"/>
       <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="n">
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="n">
         <v>0.07307042667254167</v>
       </c>
     </row>
@@ -2090,12 +2124,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SS0803</t>
+          <t>SS0501</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2178,41 +2212,41 @@
           <t>Eastern Equatoria</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>Kapoeta East</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
         <v>3</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>SS02</t>
+        </is>
       </c>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>Protests ---- Violence against civilians ---- Riots</t>
+          <t>Riots ---- Violence against civilians ---- Protests</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>Protest with intervention ---- Attack ---- Mob violence</t>
+          <t>Mob violence ---- Attack ---- Protest with intervention</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>Protesters (South Sudan) ---- Unidentified Communal Militia (South Sudan) ---- Rioters (South Sudan)</t>
+          <t>Rioters (South Sudan) ---- Unidentified Communal Militia (South Sudan) ---- Protesters (South Sudan)</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Students (South Sudan) ---- Toposa Ethnic Group (South Sudan)</t>
+          <t>Toposa Ethnic Group (South Sudan) ---- Students (South Sudan)</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>Police Forces of South Sudan (2011-) ---- Civilians (South Sudan) ---- Rioters (South Sudan)</t>
+          <t>Rioters (South Sudan) ---- Civilians (South Sudan) ---- Police Forces of South Sudan (2011-)</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -2222,15 +2256,20 @@
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>On 23 September 2024, students from the chapel school protested against school authorities after their teachers had been suspended at New Site, Northern Bari Payam (Kapoeta East County, Eastern Equatoria). The students clashed with the security personnel (coded as police officers). Six people were injured, including a student. ---- On 27 May 2024, unidentified armed assailants (coded as unidentified communal militia) shot at 2 vehicles carrying school children from Kapoeta Town to Narus along the Kapoeta-Narus Road in Kakuti area of Katordori Payam (Kapoeta East, Eastern Equatoria). The drivers drove through the ambush and the bullets damaged the vehicle, there were no casualties. Police later responded to the incident after the assailants had fled. Motivation unknown/not reported. ---- On 15 April 2024, more than 10 people, including parents and relatives of an 11-year-old student (girl), from the Toposa community confronted teachers at St. Bakhita Girl's School in Narus (Kapoeta East county, Eastern Equatoria state). The rioters hurled stones and wielded sticks in their efforts to forcibly remove the girl from the school premises to be married. They were unsuccessful in taking the girl. Police were deployed to restore calm (no interaction reported). Extent of injuries not reported/unknown.</t>
+          <t>On 15 April 2024, more than 10 people, including parents and relatives of an 11-year-old student (girl), from the Toposa community confronted teachers at St. Bakhita Girl's School in Narus (Kapoeta East county, Eastern Equatoria state). The rioters hurled stones and wielded sticks in their efforts to forcibly remove the girl from the school premises to be married. They were unsuccessful in taking the girl. Police were deployed to restore calm (no interaction reported). Extent of injuries not reported/unknown. ---- On 27 May 2024, unidentified armed assailants (coded as unidentified communal militia) shot at 2 vehicles carrying school children from Kapoeta Town to Narus along the Kapoeta-Narus Road in Kakuti area of Katordori Payam (Kapoeta East, Eastern Equatoria). The drivers drove through the ambush and the bullets damaged the vehicle, there were no casualties. Police later responded to the incident after the assailants had fled. Motivation unknown/not reported. ---- On 23 September 2024, students from the chapel school protested against school authorities after their teachers had been suspended at New Site, Northern Bari Payam (Kapoeta East County, Eastern Equatoria). The students clashed with the security personnel (coded as police officers). Six people were injured, including a student.</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>23 September 2024 ---- 27 May 2024 ---- 15 April 2024</t>
-        </is>
-      </c>
-      <c r="BL11" t="n">
+          <t>2024-04-15 ---- 2024-05-27 ---- 2024-09-23</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>Kapoeta East</t>
+        </is>
+      </c>
+      <c r="BM11" t="n">
         <v>0.01282974405969758</v>
       </c>
     </row>
@@ -2251,7 +2290,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2342,7 +2381,8 @@
       <c r="BI12" t="inlineStr"/>
       <c r="BJ12" t="inlineStr"/>
       <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="n">
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="n">
         <v>0.05948806249081326</v>
       </c>
     </row>
@@ -2454,7 +2494,8 @@
       <c r="BI13" t="inlineStr"/>
       <c r="BJ13" t="inlineStr"/>
       <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="n">
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="n">
         <v>0.05046972105795635</v>
       </c>
     </row>
@@ -2470,12 +2511,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SS0608</t>
+          <t>SS0103</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2566,7 +2607,8 @@
       <c r="BI14" t="inlineStr"/>
       <c r="BJ14" t="inlineStr"/>
       <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="n">
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="n">
         <v>0.05930218805440568</v>
       </c>
     </row>
@@ -2587,7 +2629,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SS0201;SS0207;SS0300;SS0602;SS0703;SS1001;SS1005;SS1008</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2678,7 +2720,8 @@
       <c r="BI15" t="inlineStr"/>
       <c r="BJ15" t="inlineStr"/>
       <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="n">
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="n">
         <v>0.1592982206742957</v>
       </c>
     </row>
@@ -2699,7 +2742,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2790,7 +2833,8 @@
       <c r="BI16" t="inlineStr"/>
       <c r="BJ16" t="inlineStr"/>
       <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="n">
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="n">
         <v>0.04132279437405556</v>
       </c>
     </row>
@@ -2806,12 +2850,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SS0705</t>
+          <t>SS0608</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2889,20 +2933,65 @@
       <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Jonglei</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>SS03</t>
+        </is>
+      </c>
       <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>Murle Ethnic Militia (South Sudan)</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
-      <c r="BI17" t="inlineStr"/>
-      <c r="BJ17" t="inlineStr"/>
-      <c r="BK17" t="inlineStr"/>
-      <c r="BL17" t="n">
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>Civilians (South Sudan)</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Students (South Sudan)</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>On 20 July 2025, unidentified armed individuals, suspected to be members of the Murle community, ambushed a group of students walking from Ethiopia to Akobo County, along the way between Akobo East and Akobo West, in Kaikuony Boma, Diror Payam, Akobo County (location coded to Kaikuiny/Kaikueny, the nearest known location in Akobo County, Jonglei State), resulting in 2 fatalities. Motivation unknown/not reported.</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>Akobo</t>
+        </is>
+      </c>
+      <c r="BM17" t="n">
         <v>0.0791378300049095</v>
       </c>
     </row>
@@ -2923,7 +3012,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3014,7 +3103,8 @@
       <c r="BI18" t="inlineStr"/>
       <c r="BJ18" t="inlineStr"/>
       <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="n">
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="n">
         <v>0.092169501868945</v>
       </c>
     </row>
@@ -3035,7 +3125,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3118,16 +3208,16 @@
           <t>Jonglei</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>Bor South</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
         <v>1</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>SS03</t>
+        </is>
       </c>
       <c r="BC19" t="inlineStr"/>
       <c r="BD19" t="inlineStr">
@@ -3159,10 +3249,15 @@
       </c>
       <c r="BK19" t="inlineStr">
         <is>
-          <t>20 June 2024</t>
-        </is>
-      </c>
-      <c r="BL19" t="n">
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>Bor South</t>
+        </is>
+      </c>
+      <c r="BM19" t="n">
         <v>0.296735651802859</v>
       </c>
     </row>
@@ -3178,12 +3273,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SS1010</t>
+          <t>SS0310</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3274,7 +3369,8 @@
       <c r="BI20" t="inlineStr"/>
       <c r="BJ20" t="inlineStr"/>
       <c r="BK20" t="inlineStr"/>
-      <c r="BL20" t="n">
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="n">
         <v>0.3386086896360869</v>
       </c>
     </row>
@@ -3290,12 +3386,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SS0702</t>
+          <t>SS0901</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3373,20 +3469,65 @@
       <c r="AV21" t="inlineStr"/>
       <c r="AW21" t="inlineStr"/>
       <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Jonglei</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>SS03</t>
+        </is>
+      </c>
       <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr"/>
-      <c r="BF21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>Air/drone strike</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>Military Forces of South Sudan (2011-)</t>
+        </is>
+      </c>
       <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="inlineStr"/>
-      <c r="BI21" t="inlineStr"/>
-      <c r="BJ21" t="inlineStr"/>
-      <c r="BK21" t="inlineStr"/>
-      <c r="BL21" t="n">
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>Civilians (South Sudan)</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Teachers (South Sudan)</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>On 14 June 2025, government forces (coded as SSPDF) conducted airstrikes targeting Lele, Wuntur, Kolapach, and Bariah villages in Phom Payam, New Fangak, Fangak County (location coded to New Fangak, the nearest known location in Fangak County, Jonglei State), resulting in 1 fatality, a local school teacher, while 2 cows were killed.</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>Fangak</t>
+        </is>
+      </c>
+      <c r="BM21" t="n">
         <v>0.4775064356780074</v>
       </c>
     </row>
@@ -3407,7 +3548,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3490,16 +3631,16 @@
           <t>Jonglei</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>Nyirol</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>3</v>
       </c>
       <c r="BA22" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB22" t="n">
         <v>1</v>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>SS03</t>
+        </is>
       </c>
       <c r="BC22" t="inlineStr"/>
       <c r="BD22" t="inlineStr">
@@ -3535,10 +3676,15 @@
       </c>
       <c r="BK22" t="inlineStr">
         <is>
-          <t>21 September 2024</t>
-        </is>
-      </c>
-      <c r="BL22" t="n">
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>Nyirol</t>
+        </is>
+      </c>
+      <c r="BM22" t="n">
         <v>0.2813082618654451</v>
       </c>
     </row>
@@ -3559,7 +3705,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3642,16 +3788,16 @@
           <t>Jonglei</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>Pibor</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
         <v>1</v>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>SS03</t>
+        </is>
       </c>
       <c r="BC23" t="inlineStr"/>
       <c r="BD23" t="inlineStr">
@@ -3683,10 +3829,15 @@
       </c>
       <c r="BK23" t="inlineStr">
         <is>
-          <t>14 June 2024</t>
-        </is>
-      </c>
-      <c r="BL23" t="n">
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>Pibor</t>
+        </is>
+      </c>
+      <c r="BM23" t="n">
         <v>0.1599265037018356</v>
       </c>
     </row>
@@ -3707,7 +3858,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3790,16 +3941,16 @@
           <t>Jonglei</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>Pochalla</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1</v>
       </c>
       <c r="BA24" t="n">
         <v>1</v>
       </c>
-      <c r="BB24" t="n">
-        <v>1</v>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>SS03</t>
+        </is>
       </c>
       <c r="BC24" t="inlineStr"/>
       <c r="BD24" t="inlineStr">
@@ -3835,10 +3986,15 @@
       </c>
       <c r="BK24" t="inlineStr">
         <is>
-          <t>13 July 2024</t>
-        </is>
-      </c>
-      <c r="BL24" t="n">
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>Pochalla</t>
+        </is>
+      </c>
+      <c r="BM24" t="n">
         <v>0.2086060606060606</v>
       </c>
     </row>
@@ -3859,7 +4015,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3950,7 +4106,8 @@
       <c r="BI25" t="inlineStr"/>
       <c r="BJ25" t="inlineStr"/>
       <c r="BK25" t="inlineStr"/>
-      <c r="BL25" t="n">
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="n">
         <v>0.1717686573760349</v>
       </c>
     </row>
@@ -3971,7 +4128,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4062,7 +4219,8 @@
       <c r="BI26" t="inlineStr"/>
       <c r="BJ26" t="inlineStr"/>
       <c r="BK26" t="inlineStr"/>
-      <c r="BL26" t="n">
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="n">
         <v>0.1053232807859264</v>
       </c>
     </row>
@@ -4083,7 +4241,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4174,7 +4332,8 @@
       <c r="BI27" t="inlineStr"/>
       <c r="BJ27" t="inlineStr"/>
       <c r="BK27" t="inlineStr"/>
-      <c r="BL27" t="n">
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="n">
         <v>0.3498908001371767</v>
       </c>
     </row>
@@ -4195,7 +4354,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4286,7 +4445,8 @@
       <c r="BI28" t="inlineStr"/>
       <c r="BJ28" t="inlineStr"/>
       <c r="BK28" t="inlineStr"/>
-      <c r="BL28" t="n">
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="n">
         <v>0.03575368969762868</v>
       </c>
     </row>
@@ -4307,7 +4467,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4358,31 +4518,97 @@
       <c r="W29" t="n">
         <v>0</v>
       </c>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>May 2025: Four educators were arrested following an order by the Lakes State governor, who accused them of inciting students to strike. Lectures were temporarily suspended until they were released five days later.</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>Freed</t>
+        </is>
+      </c>
       <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="inlineStr"/>
       <c r="AY29" t="inlineStr">
@@ -4390,16 +4616,16 @@
           <t>Lakes</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>Rumbek Centre</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
         <v>3</v>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>SS04</t>
+        </is>
       </c>
       <c r="BC29" t="inlineStr"/>
       <c r="BD29" t="inlineStr">
@@ -4419,22 +4645,27 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>Students (South Sudan) ---- Labor Group (South Sudan); Teachers (South Sudan) ---- Government of South Sudan (2011-); Labor Group (South Sudan); Teachers (South Sudan)</t>
+          <t>Government of South Sudan (2011-); Labor Group (South Sudan); Teachers (South Sudan) ---- Labor Group (South Sudan); Teachers (South Sudan) ---- Students (South Sudan)</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr"/>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>On 4 November 2024, an unspecified number of students at the Rumbek University of Science and Technology (RUST) held a protest at the institution in Rumbek (Rumbek Centre, Lakes), issuing a 1 week ultimatum to the government to pay academic and non-academic staff their salary arrears so that learning can resume. ---- On 4 July 2024, University of Bahr El Ghazal staff staged a protest over salary arrears in Rumbek (Rumbek Town, Rumbek Centre, Lakes). ---- On 2 July 2024, several academic staff from Rumbek University of Science and Technology, along with civil servants, peacefully marched on the streets of Rumbek in Rumbek Town (Rumbek Centre county, Lakes state), demanding eight months of unpaid salaries and five years of medical and flight allowances.</t>
+          <t>On 2 July 2024, several academic staff from Rumbek University of Science and Technology, along with civil servants, peacefully marched on the streets of Rumbek in Rumbek Town (Rumbek Centre county, Lakes state), demanding eight months of unpaid salaries and five years of medical and flight allowances. ---- On 4 July 2024, University of Bahr El Ghazal staff staged a protest over salary arrears in Rumbek (Rumbek Town, Rumbek Centre, Lakes). ---- On 4 November 2024, an unspecified number of students at the Rumbek University of Science and Technology (RUST) held a protest at the institution in Rumbek (Rumbek Centre, Lakes), issuing a 1 week ultimatum to the government to pay academic and non-academic staff their salary arrears so that learning can resume.</t>
         </is>
       </c>
       <c r="BK29" t="inlineStr">
         <is>
-          <t>04 November 2024 ---- 04 July 2024 ---- 02 July 2024</t>
-        </is>
-      </c>
-      <c r="BL29" t="n">
+          <t>2024-07-02 ---- 2024-07-04 ---- 2024-11-04</t>
+        </is>
+      </c>
+      <c r="BL29" t="inlineStr">
+        <is>
+          <t>Rumbek Centre</t>
+        </is>
+      </c>
+      <c r="BM29" t="n">
         <v>0.01444048056240491</v>
       </c>
     </row>
@@ -4455,7 +4686,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4546,7 +4777,8 @@
       <c r="BI30" t="inlineStr"/>
       <c r="BJ30" t="inlineStr"/>
       <c r="BK30" t="inlineStr"/>
-      <c r="BL30" t="n">
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="n">
         <v>0.04465449206203542</v>
       </c>
     </row>
@@ -4567,7 +4799,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4650,16 +4882,16 @@
           <t>Lakes</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>Rumbek North</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2</v>
       </c>
       <c r="BA31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB31" t="n">
         <v>1</v>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>SS04</t>
+        </is>
       </c>
       <c r="BC31" t="inlineStr"/>
       <c r="BD31" t="inlineStr">
@@ -4699,10 +4931,15 @@
       </c>
       <c r="BK31" t="inlineStr">
         <is>
-          <t>23 February 2025</t>
-        </is>
-      </c>
-      <c r="BL31" t="n">
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="BL31" t="inlineStr">
+        <is>
+          <t>Rumbek North</t>
+        </is>
+      </c>
+      <c r="BM31" t="n">
         <v>0.3019677581474465</v>
       </c>
     </row>
@@ -4723,7 +4960,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4814,7 +5051,8 @@
       <c r="BI32" t="inlineStr"/>
       <c r="BJ32" t="inlineStr"/>
       <c r="BK32" t="inlineStr"/>
-      <c r="BL32" t="n">
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="n">
         <v>0.1359521776259607</v>
       </c>
     </row>
@@ -4835,7 +5073,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -4926,7 +5164,8 @@
       <c r="BI33" t="inlineStr"/>
       <c r="BJ33" t="inlineStr"/>
       <c r="BK33" t="inlineStr"/>
-      <c r="BL33" t="n">
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="n">
         <v>0.1611145454129176</v>
       </c>
     </row>
@@ -4947,7 +5186,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5038,7 +5277,8 @@
       <c r="BI34" t="inlineStr"/>
       <c r="BJ34" t="inlineStr"/>
       <c r="BK34" t="inlineStr"/>
-      <c r="BL34" t="n">
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="n">
         <v>0.06937138099383114</v>
       </c>
     </row>
@@ -5059,7 +5299,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5137,20 +5377,65 @@
       <c r="AV35" t="inlineStr"/>
       <c r="AW35" t="inlineStr"/>
       <c r="AX35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr"/>
-      <c r="BA35" t="inlineStr"/>
-      <c r="BB35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Northern Bahr el Ghazal</t>
+        </is>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>SS05</t>
+        </is>
+      </c>
       <c r="BC35" t="inlineStr"/>
-      <c r="BD35" t="inlineStr"/>
-      <c r="BE35" t="inlineStr"/>
-      <c r="BF35" t="inlineStr"/>
-      <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>Protest with intervention</t>
+        </is>
+      </c>
+      <c r="BF35" t="inlineStr">
+        <is>
+          <t>Protesters (South Sudan)</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>Teachers (South Sudan)</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>Military Forces of South Sudan (2011-)</t>
+        </is>
+      </c>
       <c r="BI35" t="inlineStr"/>
-      <c r="BJ35" t="inlineStr"/>
-      <c r="BK35" t="inlineStr"/>
-      <c r="BL35" t="n">
+      <c r="BJ35" t="inlineStr">
+        <is>
+          <t>On 23 July 2025, a group of officials from the Teachers Association protested in Aroyo Payam, Aweil Centre County (location coded to Aroyo, the nearest known location in Aweil Centre County, Northern Bahr el Ghazal State), over the non-payment of salaries. A scuffle ensued between the protesters and officials, leading to the arrest of 12 protesters by government security forces (coded as SSPDF), while 4 people were injured.</t>
+        </is>
+      </c>
+      <c r="BK35" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="BL35" t="inlineStr">
+        <is>
+          <t>Aweil Centre</t>
+        </is>
+      </c>
+      <c r="BM35" t="n">
         <v>0.09943908947339759</v>
       </c>
     </row>
@@ -5171,7 +5456,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -5262,7 +5547,8 @@
       <c r="BI36" t="inlineStr"/>
       <c r="BJ36" t="inlineStr"/>
       <c r="BK36" t="inlineStr"/>
-      <c r="BL36" t="n">
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="n">
         <v>0.06411057425302677</v>
       </c>
     </row>
@@ -5278,12 +5564,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SS0711</t>
+          <t>SS0308</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5374,7 +5660,8 @@
       <c r="BI37" t="inlineStr"/>
       <c r="BJ37" t="inlineStr"/>
       <c r="BK37" t="inlineStr"/>
-      <c r="BL37" t="n">
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5395,7 +5682,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5486,7 +5773,8 @@
       <c r="BI38" t="inlineStr"/>
       <c r="BJ38" t="inlineStr"/>
       <c r="BK38" t="inlineStr"/>
-      <c r="BL38" t="n">
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="n">
         <v>0.05035728893486996</v>
       </c>
     </row>
@@ -5507,7 +5795,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5656,31 +5944,31 @@
           <t>Northern Bahr el Ghazal</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>Aweil West</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB39" t="n">
         <v>2</v>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>SS05</t>
+        </is>
       </c>
       <c r="BC39" t="inlineStr"/>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>Protests ---- Riots</t>
+          <t>Riots ---- Protests</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Violent demonstration</t>
+          <t>Violent demonstration ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>Protesters (South Sudan) ---- Rioters (South Sudan)</t>
+          <t>Rioters (South Sudan) ---- Protesters (South Sudan)</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
@@ -5696,15 +5984,20 @@
       <c r="BI39" t="inlineStr"/>
       <c r="BJ39" t="inlineStr">
         <is>
-          <t>On 13 January 2024, approximately 60 teachers protested in front of the UNMISS Aweil Field Office compound in Aweil Town (Aweil West, Northern Bahr el Ghazal) against the alleged reduction of their salaries by the government and the arrest of three teachers during a similar protest on 12 January 2024 (coded separately). The protesters dispersed later after handing over a petition to the UNMISS representative. ---- On 12 January 2024, teachers held a demonstration in Aweil (Aweil West county, Northern Bahr el Ghazal state) against an alleged deduction of their salaries. Rioters pelted stones at military police officers, injuring some of them, and vandalized the Ministry of General Education office. Police responded by beating demonstrators, resulting in at least 30 injuries, and arresting between 27 to 300 teachers. Demonstrators denied allegations of vandalism. Extent of injuries unknown/not reported.</t>
+          <t>On 12 January 2024, teachers held a demonstration in Aweil (Aweil West county, Northern Bahr el Ghazal state) against an alleged deduction of their salaries. Rioters pelted stones at military police officers, injuring some of them, and vandalized the Ministry of General Education office. Police responded by beating demonstrators, resulting in at least 30 injuries, and arresting between 27 to 300 teachers. Demonstrators denied allegations of vandalism. Extent of injuries unknown/not reported. ---- On 13 January 2024, approximately 60 teachers protested in front of the UNMISS Aweil Field Office compound in Aweil Town (Aweil West, Northern Bahr el Ghazal) against the alleged reduction of their salaries by the government and the arrest of three teachers during a similar protest on 12 January 2024 (coded separately). The protesters dispersed later after handing over a petition to the UNMISS representative.</t>
         </is>
       </c>
       <c r="BK39" t="inlineStr">
         <is>
-          <t>13 January 2024 ---- 12 January 2024</t>
-        </is>
-      </c>
-      <c r="BL39" t="n">
+          <t>2024-01-12 ---- 2024-01-13</t>
+        </is>
+      </c>
+      <c r="BL39" t="inlineStr">
+        <is>
+          <t>Aweil West</t>
+        </is>
+      </c>
+      <c r="BM39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5725,7 +6018,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -5816,7 +6109,8 @@
       <c r="BI40" t="inlineStr"/>
       <c r="BJ40" t="inlineStr"/>
       <c r="BK40" t="inlineStr"/>
-      <c r="BL40" t="n">
+      <c r="BL40" t="inlineStr"/>
+      <c r="BM40" t="n">
         <v>0.1433748037202561</v>
       </c>
     </row>
@@ -5832,12 +6126,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SS0201</t>
+          <t>SS0504</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SS0201;SS0207;SS0300;SS0602;SS0703;SS1001;SS1005;SS1008</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5928,7 +6222,8 @@
       <c r="BI41" t="inlineStr"/>
       <c r="BJ41" t="inlineStr"/>
       <c r="BK41" t="inlineStr"/>
-      <c r="BL41" t="n">
+      <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="n">
         <v>0.3857105987611837</v>
       </c>
     </row>
@@ -5944,12 +6239,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SS0106</t>
+          <t>SS0104</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -6040,7 +6335,8 @@
       <c r="BI42" t="inlineStr"/>
       <c r="BJ42" t="inlineStr"/>
       <c r="BK42" t="inlineStr"/>
-      <c r="BL42" t="n">
+      <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="n">
         <v>0.2620501420974141</v>
       </c>
     </row>
@@ -6061,7 +6357,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6152,7 +6448,8 @@
       <c r="BI43" t="inlineStr"/>
       <c r="BJ43" t="inlineStr"/>
       <c r="BK43" t="inlineStr"/>
-      <c r="BL43" t="n">
+      <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="n">
         <v>0.4728706847764573</v>
       </c>
     </row>
@@ -6173,7 +6470,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6264,7 +6561,8 @@
       <c r="BI44" t="inlineStr"/>
       <c r="BJ44" t="inlineStr"/>
       <c r="BK44" t="inlineStr"/>
-      <c r="BL44" t="n">
+      <c r="BL44" t="inlineStr"/>
+      <c r="BM44" t="n">
         <v>0.4060030935161574</v>
       </c>
     </row>
@@ -6285,7 +6583,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6376,7 +6674,8 @@
       <c r="BI45" t="inlineStr"/>
       <c r="BJ45" t="inlineStr"/>
       <c r="BK45" t="inlineStr"/>
-      <c r="BL45" t="n">
+      <c r="BL45" t="inlineStr"/>
+      <c r="BM45" t="n">
         <v>0.2397808198254959</v>
       </c>
     </row>
@@ -6397,7 +6696,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6488,7 +6787,8 @@
       <c r="BI46" t="inlineStr"/>
       <c r="BJ46" t="inlineStr"/>
       <c r="BK46" t="inlineStr"/>
-      <c r="BL46" t="n">
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="n">
         <v>0.2556860130034057</v>
       </c>
     </row>
@@ -6504,12 +6804,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SS0206</t>
+          <t>SS0804</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -6600,7 +6900,8 @@
       <c r="BI47" t="inlineStr"/>
       <c r="BJ47" t="inlineStr"/>
       <c r="BK47" t="inlineStr"/>
-      <c r="BL47" t="n">
+      <c r="BL47" t="inlineStr"/>
+      <c r="BM47" t="n">
         <v>0.08937584328619259</v>
       </c>
     </row>
@@ -6621,7 +6922,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -6712,7 +7013,8 @@
       <c r="BI48" t="inlineStr"/>
       <c r="BJ48" t="inlineStr"/>
       <c r="BK48" t="inlineStr"/>
-      <c r="BL48" t="n">
+      <c r="BL48" t="inlineStr"/>
+      <c r="BM48" t="n">
         <v>0.6797961802254202</v>
       </c>
     </row>
@@ -6733,7 +7035,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -6824,7 +7126,8 @@
       <c r="BI49" t="inlineStr"/>
       <c r="BJ49" t="inlineStr"/>
       <c r="BK49" t="inlineStr"/>
-      <c r="BL49" t="n">
+      <c r="BL49" t="inlineStr"/>
+      <c r="BM49" t="n">
         <v>0.07426384745103126</v>
       </c>
     </row>
@@ -6840,12 +7143,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SS0306</t>
+          <t>SS1010</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -6936,7 +7239,8 @@
       <c r="BI50" t="inlineStr"/>
       <c r="BJ50" t="inlineStr"/>
       <c r="BK50" t="inlineStr"/>
-      <c r="BL50" t="n">
+      <c r="BL50" t="inlineStr"/>
+      <c r="BM50" t="n">
         <v>0.1481275078020508</v>
       </c>
     </row>
@@ -6957,7 +7261,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SS0201;SS0207;SS0300;SS0602;SS0703;SS1001;SS1005;SS1008</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -7048,7 +7352,8 @@
       <c r="BI51" t="inlineStr"/>
       <c r="BJ51" t="inlineStr"/>
       <c r="BK51" t="inlineStr"/>
-      <c r="BL51" t="n">
+      <c r="BL51" t="inlineStr"/>
+      <c r="BM51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7064,12 +7369,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SS0609</t>
+          <t>SS0311</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -7152,26 +7457,26 @@
           <t>Upper Nile</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>Luakpiny/Nasir</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>5</v>
       </c>
       <c r="BA52" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB52" t="n">
         <v>2</v>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>SS07</t>
+        </is>
       </c>
       <c r="BC52" t="inlineStr"/>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>Battles ---- Violence against civilians</t>
+          <t>Violence against civilians ---- Battles</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>Armed clash ---- Attack</t>
+          <t>Attack ---- Armed clash</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
@@ -7182,7 +7487,7 @@
       <c r="BG52" t="inlineStr"/>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>Nuer Ethnic Militia (South Sudan) ---- Civilians (South Sudan)</t>
+          <t>Civilians (South Sudan) ---- Nuer Ethnic Militia (South Sudan)</t>
         </is>
       </c>
       <c r="BI52" t="inlineStr">
@@ -7192,15 +7497,20 @@
       </c>
       <c r="BJ52" t="inlineStr">
         <is>
-          <t>On 14 August 2024, SSPDF clashed with gunmen described as 'White Army' (coded as Nuer) in Nasir (Luakpiny/Nasir, Upper Nile). 4 people were killed (including 3 SSPDF), another was injured, and civilians were displaced. SSPDF shelling was reported. The violence was triggered by the killing of a student on August 11 near Kaajiok-Wecyaradiw (coded separately). The SSPDF spokesperson denied that the national army clashed with the White Army, stating instead that they engaged with an unidentified armed group. ---- On 11 August 2024, individuals wearing military uniforms (coded as SSPDF) ambushed and killed a student traveling from Ethiopia to Ulang County at Kaajiok- Wecyaradiw village in Mading payam (location coded to Mading, Luakpiny/Nasir county, Upper Nile state). Motivation unknown/not reported.</t>
+          <t>On 11 August 2024, individuals wearing military uniforms (coded as SSPDF) ambushed and killed a student traveling from Ethiopia to Ulang County at Kaajiok- Wecyaradiw village in Mading payam (location coded to Mading, Luakpiny/Nasir county, Upper Nile state). Motivation unknown/not reported. ---- On 14 August 2024, SSPDF clashed with gunmen described as 'White Army' (coded as Nuer) in Nasir (Luakpiny/Nasir, Upper Nile). 4 people were killed (including 3 SSPDF), another was injured, and civilians were displaced. SSPDF shelling was reported. The violence was triggered by the killing of a student on August 11 near Kaajiok-Wecyaradiw (coded separately). The SSPDF spokesperson denied that the national army clashed with the White Army, stating instead that they engaged with an unidentified armed group.</t>
         </is>
       </c>
       <c r="BK52" t="inlineStr">
         <is>
-          <t>14 August 2024 ---- 11 August 2024</t>
-        </is>
-      </c>
-      <c r="BL52" t="n">
+          <t>2024-08-11 ---- 2024-08-14</t>
+        </is>
+      </c>
+      <c r="BL52" t="inlineStr">
+        <is>
+          <t>Luakpiny/Nasir</t>
+        </is>
+      </c>
+      <c r="BM52" t="n">
         <v>0.0106654677979396</v>
       </c>
     </row>
@@ -7221,7 +7531,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -7312,7 +7622,8 @@
       <c r="BI53" t="inlineStr"/>
       <c r="BJ53" t="inlineStr"/>
       <c r="BK53" t="inlineStr"/>
-      <c r="BL53" t="n">
+      <c r="BL53" t="inlineStr"/>
+      <c r="BM53" t="n">
         <v>0.04562597737098703</v>
       </c>
     </row>
@@ -7328,12 +7639,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SS0208</t>
+          <t>SS0300</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0300;SS0706</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -7424,7 +7735,8 @@
       <c r="BI54" t="inlineStr"/>
       <c r="BJ54" t="inlineStr"/>
       <c r="BK54" t="inlineStr"/>
-      <c r="BL54" t="n">
+      <c r="BL54" t="inlineStr"/>
+      <c r="BM54" t="n">
         <v>0.003270841643398484</v>
       </c>
     </row>
@@ -7445,7 +7757,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -7528,16 +7840,16 @@
           <t>Upper Nile</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>Malakal</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>0</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB55" t="n">
         <v>1</v>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>SS07</t>
+        </is>
       </c>
       <c r="BC55" t="inlineStr"/>
       <c r="BD55" t="inlineStr">
@@ -7565,10 +7877,15 @@
       </c>
       <c r="BK55" t="inlineStr">
         <is>
-          <t>12 June 2024</t>
-        </is>
-      </c>
-      <c r="BL55" t="n">
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="BL55" t="inlineStr">
+        <is>
+          <t>Malakal</t>
+        </is>
+      </c>
+      <c r="BM55" t="n">
         <v>0.489396074657134</v>
       </c>
     </row>
@@ -7589,7 +7906,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -7680,7 +7997,8 @@
       <c r="BI56" t="inlineStr"/>
       <c r="BJ56" t="inlineStr"/>
       <c r="BK56" t="inlineStr"/>
-      <c r="BL56" t="n">
+      <c r="BL56" t="inlineStr"/>
+      <c r="BM56" t="n">
         <v>0.1754882870124506</v>
       </c>
     </row>
@@ -7701,7 +8019,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -7792,7 +8110,8 @@
       <c r="BI57" t="inlineStr"/>
       <c r="BJ57" t="inlineStr"/>
       <c r="BK57" t="inlineStr"/>
-      <c r="BL57" t="n">
+      <c r="BL57" t="inlineStr"/>
+      <c r="BM57" t="n">
         <v>0.2803595206391478</v>
       </c>
     </row>
@@ -7904,7 +8223,8 @@
       <c r="BI58" t="inlineStr"/>
       <c r="BJ58" t="inlineStr"/>
       <c r="BK58" t="inlineStr"/>
-      <c r="BL58" t="n">
+      <c r="BL58" t="inlineStr"/>
+      <c r="BM58" t="n">
         <v>0.2026529821843532</v>
       </c>
     </row>
@@ -7925,7 +8245,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -8016,7 +8336,8 @@
       <c r="BI59" t="inlineStr"/>
       <c r="BJ59" t="inlineStr"/>
       <c r="BK59" t="inlineStr"/>
-      <c r="BL59" t="n">
+      <c r="BL59" t="inlineStr"/>
+      <c r="BM59" t="n">
         <v>0.2504401060565779</v>
       </c>
     </row>
@@ -8032,12 +8353,12 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SS1006</t>
+          <t>SS1010</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -8128,7 +8449,8 @@
       <c r="BI60" t="inlineStr"/>
       <c r="BJ60" t="inlineStr"/>
       <c r="BK60" t="inlineStr"/>
-      <c r="BL60" t="n">
+      <c r="BL60" t="inlineStr"/>
+      <c r="BM60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8149,7 +8471,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -8240,7 +8562,8 @@
       <c r="BI61" t="inlineStr"/>
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
-      <c r="BL61" t="n">
+      <c r="BL61" t="inlineStr"/>
+      <c r="BM61" t="n">
         <v>0.1135861167241174</v>
       </c>
     </row>
@@ -8261,7 +8584,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -8352,7 +8675,8 @@
       <c r="BI62" t="inlineStr"/>
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
-      <c r="BL62" t="n">
+      <c r="BL62" t="inlineStr"/>
+      <c r="BM62" t="n">
         <v>0.06310365891445417</v>
       </c>
     </row>
@@ -8368,12 +8692,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SS0203</t>
+          <t>SS0804</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -8464,7 +8788,8 @@
       <c r="BI63" t="inlineStr"/>
       <c r="BJ63" t="inlineStr"/>
       <c r="BK63" t="inlineStr"/>
-      <c r="BL63" t="n">
+      <c r="BL63" t="inlineStr"/>
+      <c r="BM63" t="n">
         <v>0.09966586955809612</v>
       </c>
     </row>
@@ -8480,12 +8805,12 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SS0202</t>
+          <t>SS0608</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -8576,7 +8901,8 @@
       <c r="BI64" t="inlineStr"/>
       <c r="BJ64" t="inlineStr"/>
       <c r="BK64" t="inlineStr"/>
-      <c r="BL64" t="n">
+      <c r="BL64" t="inlineStr"/>
+      <c r="BM64" t="n">
         <v>0.1097020666967341</v>
       </c>
     </row>
@@ -8597,7 +8923,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -8688,7 +9014,8 @@
       <c r="BI65" t="inlineStr"/>
       <c r="BJ65" t="inlineStr"/>
       <c r="BK65" t="inlineStr"/>
-      <c r="BL65" t="n">
+      <c r="BL65" t="inlineStr"/>
+      <c r="BM65" t="n">
         <v>0.06041230001857207</v>
       </c>
     </row>
@@ -8709,7 +9036,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -8854,16 +9181,16 @@
           <t>Warrap</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>Twic</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>3</v>
       </c>
       <c r="BA66" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB66" t="n">
         <v>1</v>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>SS08</t>
+        </is>
       </c>
       <c r="BC66" t="inlineStr"/>
       <c r="BD66" t="inlineStr">
@@ -8903,10 +9230,15 @@
       </c>
       <c r="BK66" t="inlineStr">
         <is>
-          <t>19 January 2024</t>
-        </is>
-      </c>
-      <c r="BL66" t="n">
+          <t>2024-01-19</t>
+        </is>
+      </c>
+      <c r="BL66" t="inlineStr">
+        <is>
+          <t>Twic</t>
+        </is>
+      </c>
+      <c r="BM66" t="n">
         <v>0.2172215552497243</v>
       </c>
     </row>
@@ -8927,7 +9259,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -9018,7 +9350,8 @@
       <c r="BI67" t="inlineStr"/>
       <c r="BJ67" t="inlineStr"/>
       <c r="BK67" t="inlineStr"/>
-      <c r="BL67" t="n">
+      <c r="BL67" t="inlineStr"/>
+      <c r="BM67" t="n">
         <v>0.06754930201639707</v>
       </c>
     </row>
@@ -9039,7 +9372,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -9130,7 +9463,8 @@
       <c r="BI68" t="inlineStr"/>
       <c r="BJ68" t="inlineStr"/>
       <c r="BK68" t="inlineStr"/>
-      <c r="BL68" t="n">
+      <c r="BL68" t="inlineStr"/>
+      <c r="BM68" t="n">
         <v>0.02304980842911877</v>
       </c>
     </row>
@@ -9151,7 +9485,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -9234,51 +9568,56 @@
           <t>Western Bahr el Ghazal</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>Wau</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>0</v>
       </c>
       <c r="BA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB69" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>SS09</t>
+        </is>
       </c>
       <c r="BC69" t="inlineStr"/>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>Protests ---- Protests</t>
+          <t>Protests ---- Protests ---- Protests</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Peaceful protest</t>
+          <t>Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>Protesters (South Sudan) ---- Protesters (South Sudan)</t>
+          <t>Protesters (South Sudan) ---- Protesters (South Sudan) ---- Protesters (South Sudan)</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>Teachers (South Sudan) ---- Students (South Sudan)</t>
+          <t>Students (South Sudan) ---- Teachers (South Sudan) ---- Students (South Sudan)</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr"/>
       <c r="BI69" t="inlineStr"/>
       <c r="BJ69" t="inlineStr">
         <is>
-          <t>On 4 July 2024, lecturers at the University of Bahr el-Ghazal marched on the streets in Wau, Wau North (Wau county, Western Bahr el Ghazal state), demanding eight months of unpaid salaries and five years of medical and flight allowances. ---- On 6 May 2024, thousands of students from Western Bahr el Ghazal took to the streets around the university campus in Wau North (Wau county, Western Bahr el Ghazal state), demanding that the government fulfill its obligation to a contracted food supplier for the institution. The protesters threatened to access food by entering the main markets of the town if their demand was not met. As a result, three markets were temporarily shut down due to safety concerns, prompting the deployment of police forces near the university campus to ensure security. There was no interaction.</t>
+          <t>On 6 May 2024, thousands of students from Western Bahr el Ghazal took to the streets around the university campus in Wau North (Wau county, Western Bahr el Ghazal state), demanding that the government fulfill its obligation to a contracted food supplier for the institution. The protesters threatened to access food by entering the main markets of the town if their demand was not met. As a result, three markets were temporarily shut down due to safety concerns, prompting the deployment of police forces near the university campus to ensure security. There was no interaction. ---- On 4 July 2024, lecturers at the University of Bahr el-Ghazal marched on the streets in Wau, Wau North (Wau county, Western Bahr el Ghazal state), demanding eight months of unpaid salaries and five years of medical and flight allowances. ---- On 23 May 2025, students at the University of Bahr el Ghazal protested in Wau (Wau, Western Bahr el Ghazal), over the recent increment of fees at the institution. Security personnel were deployed to the scene but did not interfere. The university administration later closed the institution indefinitely.</t>
         </is>
       </c>
       <c r="BK69" t="inlineStr">
         <is>
-          <t>04 July 2024 ---- 06 May 2024</t>
-        </is>
-      </c>
-      <c r="BL69" t="n">
+          <t>2024-05-06 ---- 2024-07-04 ---- 2025-05-23</t>
+        </is>
+      </c>
+      <c r="BL69" t="inlineStr">
+        <is>
+          <t>Wau</t>
+        </is>
+      </c>
+      <c r="BM69" t="n">
         <v>0.05213307594179339</v>
       </c>
     </row>
@@ -9299,7 +9638,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SS0201;SS0207;SS0300;SS0602;SS0703;SS1001;SS1005;SS1008</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -9390,7 +9729,8 @@
       <c r="BI70" t="inlineStr"/>
       <c r="BJ70" t="inlineStr"/>
       <c r="BK70" t="inlineStr"/>
-      <c r="BL70" t="n">
+      <c r="BL70" t="inlineStr"/>
+      <c r="BM70" t="n">
         <v>0.1727505644199792</v>
       </c>
     </row>
@@ -9411,7 +9751,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -9489,20 +9829,61 @@
       <c r="AV71" t="inlineStr"/>
       <c r="AW71" t="inlineStr"/>
       <c r="AX71" t="inlineStr"/>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr"/>
-      <c r="BA71" t="inlineStr"/>
-      <c r="BB71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Western Equatoria</t>
+        </is>
+      </c>
+      <c r="AZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>SS10</t>
+        </is>
+      </c>
       <c r="BC71" t="inlineStr"/>
-      <c r="BD71" t="inlineStr"/>
-      <c r="BE71" t="inlineStr"/>
-      <c r="BF71" t="inlineStr"/>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>Battles</t>
+        </is>
+      </c>
+      <c r="BE71" t="inlineStr">
+        <is>
+          <t>Armed clash</t>
+        </is>
+      </c>
+      <c r="BF71" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (South Sudan)</t>
+        </is>
+      </c>
       <c r="BG71" t="inlineStr"/>
-      <c r="BH71" t="inlineStr"/>
+      <c r="BH71" t="inlineStr">
+        <is>
+          <t>Military Forces of South Sudan (2011-)</t>
+        </is>
+      </c>
       <c r="BI71" t="inlineStr"/>
-      <c r="BJ71" t="inlineStr"/>
-      <c r="BK71" t="inlineStr"/>
-      <c r="BL71" t="n">
+      <c r="BJ71" t="inlineStr">
+        <is>
+          <t>On 22 May 2025, unidentified armed assailants (coded as unidentified armed group) clashed with SSPDF forces at a military outpost in Nabanga Primary School, Nabanga Payam, Ibba County (Ibba, Western Equatoria). The clash ensued after the assailants ambushed the outpost, but were repelled. Motivation unknown/not reported. Casualties unknown.</t>
+        </is>
+      </c>
+      <c r="BK71" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="BL71" t="inlineStr">
+        <is>
+          <t>Ibba</t>
+        </is>
+      </c>
+      <c r="BM71" t="n">
         <v>0.1092027559055118</v>
       </c>
     </row>
@@ -9523,7 +9904,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0101;SS0104;SS0105;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0306;SS0307;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0608;SS0609;SS0705;SS0707;SS0709;SS0801;SS0803;SS0804;SS0806;SS0901;SS0903;SS1003</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -9614,7 +9995,8 @@
       <c r="BI72" t="inlineStr"/>
       <c r="BJ72" t="inlineStr"/>
       <c r="BK72" t="inlineStr"/>
-      <c r="BL72" t="n">
+      <c r="BL72" t="inlineStr"/>
+      <c r="BM72" t="n">
         <v>0.1006937289649014</v>
       </c>
     </row>
@@ -9635,7 +10017,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SS0204;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0604;SS0607;SS0701;SS0805;SS0902;SS1004</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -9726,7 +10108,8 @@
       <c r="BI73" t="inlineStr"/>
       <c r="BJ73" t="inlineStr"/>
       <c r="BK73" t="inlineStr"/>
-      <c r="BL73" t="n">
+      <c r="BL73" t="inlineStr"/>
+      <c r="BM73" t="n">
         <v>0.1425330482963222</v>
       </c>
     </row>
@@ -9747,7 +10130,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SS0201;SS0207;SS0300;SS0602;SS0703;SS1001;SS1005;SS1008</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -9838,7 +10221,8 @@
       <c r="BI74" t="inlineStr"/>
       <c r="BJ74" t="inlineStr"/>
       <c r="BK74" t="inlineStr"/>
-      <c r="BL74" t="n">
+      <c r="BL74" t="inlineStr"/>
+      <c r="BM74" t="n">
         <v>0.02644518272425249</v>
       </c>
     </row>
@@ -9859,7 +10243,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -9950,7 +10334,8 @@
       <c r="BI75" t="inlineStr"/>
       <c r="BJ75" t="inlineStr"/>
       <c r="BK75" t="inlineStr"/>
-      <c r="BL75" t="n">
+      <c r="BL75" t="inlineStr"/>
+      <c r="BM75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10120,16 +10505,16 @@
           <t>Western Equatoria</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>Nagero</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>2</v>
       </c>
       <c r="BA76" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB76" t="n">
         <v>1</v>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>SS10</t>
+        </is>
       </c>
       <c r="BC76" t="inlineStr"/>
       <c r="BD76" t="inlineStr">
@@ -10165,10 +10550,15 @@
       </c>
       <c r="BK76" t="inlineStr">
         <is>
-          <t>08 February 2025</t>
-        </is>
-      </c>
-      <c r="BL76" t="n">
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="BL76" t="inlineStr">
+        <is>
+          <t>Nagero</t>
+        </is>
+      </c>
+      <c r="BM76" t="n">
         <v>0.4700319186665091</v>
       </c>
     </row>
@@ -10189,7 +10579,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SS0201;SS0207;SS0300;SS0602;SS0703;SS1001;SS1005;SS1008</t>
+          <t>SS0201;SS0204;SS0207;SS0402;SS0403;SS0404;SS0407;SS0408;SS0504;SS0602;SS0604;SS0607;SS0701;SS0703;SS0805;SS0902;SS1001;SS1004;SS1005;SS1008</t>
         </is>
       </c>
       <c r="H77" t="n">
@@ -10280,7 +10670,8 @@
       <c r="BI77" t="inlineStr"/>
       <c r="BJ77" t="inlineStr"/>
       <c r="BK77" t="inlineStr"/>
-      <c r="BL77" t="n">
+      <c r="BL77" t="inlineStr"/>
+      <c r="BM77" t="n">
         <v>0.0511731843575419</v>
       </c>
     </row>
@@ -10301,7 +10692,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SS0001;SS0102;SS0103;SS0104;SS0105;SS0203;SS0206;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0608;SS0708;SS0711;SS0712;SS0803;SS1002;SS1006;SS1009</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -10392,7 +10783,8 @@
       <c r="BI78" t="inlineStr"/>
       <c r="BJ78" t="inlineStr"/>
       <c r="BK78" t="inlineStr"/>
-      <c r="BL78" t="n">
+      <c r="BL78" t="inlineStr"/>
+      <c r="BM78" t="n">
         <v>0.2393525275308478</v>
       </c>
     </row>
@@ -10408,12 +10800,12 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SS0705</t>
+          <t>SS0712</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SS0101;SS0106;SS0202;SS0208;SS0301;SS0302;SS0303;SS0305;SS0306;SS0307;SS0308;SS0309;SS0401;SS0502;SS0505;SS0601;SS0603;SS0605;SS0609;SS0702;SS0704;SS0705;SS0706;SS0707;SS0709;SS0801;SS0802;SS0804;SS0806;SS0901;SS0903;SS1003;SS1010</t>
+          <t>SS0001;SS0102;SS0103;SS0203;SS0206;SS0305;SS0308;SS0310;SS0311;SS0405;SS0406;SS0501;SS0503;SS0606;SS0702;SS0704;SS0708;SS0711;SS0712;SS0802;SS1002;SS1006;SS1009;SS1010</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -10491,20 +10883,65 @@
       <c r="AV79" t="inlineStr"/>
       <c r="AW79" t="inlineStr"/>
       <c r="AX79" t="inlineStr"/>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr"/>
-      <c r="BA79" t="inlineStr"/>
-      <c r="BB79" t="inlineStr"/>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Western Equatoria</t>
+        </is>
+      </c>
+      <c r="AZ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>SS10</t>
+        </is>
+      </c>
       <c r="BC79" t="inlineStr"/>
-      <c r="BD79" t="inlineStr"/>
-      <c r="BE79" t="inlineStr"/>
-      <c r="BF79" t="inlineStr"/>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BE79" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BF79" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (South Sudan)</t>
+        </is>
+      </c>
       <c r="BG79" t="inlineStr"/>
-      <c r="BH79" t="inlineStr"/>
-      <c r="BI79" t="inlineStr"/>
-      <c r="BJ79" t="inlineStr"/>
-      <c r="BK79" t="inlineStr"/>
-      <c r="BL79" t="n">
+      <c r="BH79" t="inlineStr">
+        <is>
+          <t>Civilians (South Sudan)</t>
+        </is>
+      </c>
+      <c r="BI79" t="inlineStr">
+        <is>
+          <t>Government of South Sudan (2011-)</t>
+        </is>
+      </c>
+      <c r="BJ79" t="inlineStr">
+        <is>
+          <t>On 2 August 2025, 3 unidentified armed assailants (coded as unidentified armed group) shot and killed the Director General of the Ministry of Education in Western Equatoria and wounded another family member at his private residence in Akorobodi area of Yambio Town, Yambio Town Payam, Yambio County (Yambio, Western Equatoria State). Motivation unknown/not reported.</t>
+        </is>
+      </c>
+      <c r="BK79" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="BL79" t="inlineStr">
+        <is>
+          <t>Yambio</t>
+        </is>
+      </c>
+      <c r="BM79" t="n">
         <v>0.05006093559576263</v>
       </c>
     </row>
@@ -10514,10 +10951,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9824523CAB29F4DA646F20BAFE41B4C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c972c102b01d47663811fb2ebdbd1e4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" xmlns:ns3="14cbb838-50ff-4dab-9c3f-cddf75f03c13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd0e8b72e466adcc572d3af37c1ebe05" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6"/>
-    <xsd:import namespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
+    <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <xsd:import namespace="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -10529,13 +10966,15 @@
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
@@ -10544,7 +10983,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4877444-78fa-4cfa-bafc-d6c64fafc061" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -10562,52 +11001,57 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="18" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d0fa6634-326e-4532-91a2-52bea7ac9212" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
@@ -10635,6 +11079,17 @@
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{d6bd4e25-e667-4943-8e38-5db701f530ee}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d0fa6634-326e-4532-91a2-52bea7ac9212">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -10748,7 +11203,8 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5940141-1bc9-4c17-b1bc-e50f6b2083d6">
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
@@ -10756,13 +11212,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C019C1A1-B033-4449-BB07-E6E9708568EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBD788C1-C87C-4211-882B-6DFF3643A6CB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BCC208B-1688-49F8-8A3E-49BC72AE265B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46164DDA-EC7C-4566-97FE-6C4004ADC6D8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD531540-39ED-4464-9B5F-47DCC259A8F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6612CC8B-B961-4734-8FF4-BBA9DBFEFF85}"/>
 </file>
--- a/context_DB/SSD_context_db.xlsx
+++ b/context_DB/SSD_context_db.xlsx
@@ -11212,13 +11212,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBD788C1-C87C-4211-882B-6DFF3643A6CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F7B71A-F21F-4393-A982-0EF608C403E6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46164DDA-EC7C-4566-97FE-6C4004ADC6D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DA5501-22D8-40DF-A430-6B7F76354D9E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6612CC8B-B961-4734-8FF4-BBA9DBFEFF85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E922294-CB3A-4A7D-A963-E7EE8E1468A4}"/>
 </file>